--- a/template.xlsx
+++ b/template.xlsx
@@ -2,19 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ЭтаКнига" defaultThemeVersion="124226"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="105" windowWidth="14355" windowHeight="7245"/>
+    <workbookView xWindow="480" yWindow="120" windowWidth="27795" windowHeight="12090"/>
   </bookViews>
   <sheets>
-    <sheet name="main" sheetId="79" r:id="rId1"/>
+    <sheet name="main" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+  <si>
+    <t>Гравець</t>
+  </si>
+  <si>
+    <t>Сума</t>
+  </si>
   <si>
     <t>Столи</t>
   </si>
@@ -25,7 +31,16 @@
     <t>По</t>
   </si>
   <si>
-    <t>Сума</t>
+    <t>Хв.</t>
+  </si>
+  <si>
+    <t>Стіл</t>
+  </si>
+  <si>
+    <t>Тариф</t>
+  </si>
+  <si>
+    <t>Пушняк</t>
   </si>
   <si>
     <t>Козин</t>
@@ -34,34 +49,22 @@
     <t>Воронцов</t>
   </si>
   <si>
+    <t>Розовецький</t>
+  </si>
+  <si>
     <t>Москаленко</t>
   </si>
   <si>
     <t>Мілевський</t>
   </si>
   <si>
-    <t>Хв.</t>
-  </si>
-  <si>
-    <t>Пушняк</t>
-  </si>
-  <si>
-    <t>Розовецький</t>
-  </si>
-  <si>
     <t>Ганушевич</t>
   </si>
   <si>
-    <t>Тариф</t>
-  </si>
-  <si>
-    <t>Стіл</t>
-  </si>
-  <si>
-    <t>Гравець</t>
-  </si>
-  <si>
     <t>Хомін</t>
+  </si>
+  <si>
+    <t>0 - 0</t>
   </si>
 </sst>
 </file>
@@ -143,7 +146,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -158,7 +161,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -188,52 +191,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -538,361 +541,422 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист75"/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="7" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" customWidth="1"/>
+    <col min="4" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="7" width="7.7109375" customWidth="1"/>
     <col min="10" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="9" t="e">
+        <f>ROUNDUP(O1*1.6, 0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="6" t="e">
+        <f>VLOOKUP(VALUE(LEFT(K1,1)),$A$15:$B$20,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M1" s="6" t="e">
+        <f>VLOOKUP(VALUE(RIGHT(K1,1)),$A$15:$C$20,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N1" s="6"/>
+      <c r="O1" s="11" t="e">
+        <f t="shared" ref="O1" si="0">HOUR(M1-L1)*60 + MINUTE(M1-L1)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="9" t="e">
+        <f>ROUNDUP(G2*1.6, 0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="6" t="e">
+        <f>VLOOKUP(VALUE(LEFT(C2,1)),$A$15:$B$20,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E2" s="6" t="e">
+        <f>VLOOKUP(VALUE(RIGHT(C2,1)),$A$15:$C$20,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="11" t="e">
+        <f t="shared" ref="G2:G8" si="1">HOUR(E2-D2)*60 + MINUTE(E2-D2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N2" s="14" t="e">
+        <f>I3-SUM(B2:B11)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="9" t="e">
+        <f t="shared" ref="B3:B8" si="2">ROUNDUP(G3*1.6, 0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="e">
+        <f t="shared" ref="D3:D8" si="3">VLOOKUP(VALUE(LEFT(C3,1)),$A$15:$B$20,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E3" s="6" t="e">
+        <f t="shared" ref="E3:E8" si="4">VLOOKUP(VALUE(RIGHT(C3,1)),$A$15:$C$20,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="9">
+        <f>SUM(E15:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="9" t="e">
+        <f>N2-J1</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E4" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E5" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E6" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B8" s="9" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E8" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="11"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="11"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="11"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="11"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14">
+        <f>HOUR(C15-B15)*60 + MINUTE(C15-B15)</f>
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="14" t="e">
-        <f>ROUNDUP(G2*1.6, 0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="18" t="e">
-        <f t="shared" ref="D2:D8" si="0">VLOOKUP(VALUE(LEFT(C2,1)),$I$2:$J$7,2,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E2" s="18" t="e">
-        <f t="shared" ref="E2:E8" si="1">VLOOKUP(VALUE(RIGHT(C2,1)),$I$2:$K$7,3,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="21" t="e">
-        <f t="shared" ref="G2:G8" si="2">HOUR(E2-D2)*60 + MINUTE(E2-D2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="4">
-        <f>HOUR(K2-J2)*60 + MINUTE(K2-J2)</f>
+      <c r="E15" s="15">
+        <f>ROUND(ROUND(D15*4, 0)*0.8, 0)</f>
         <v>0</v>
       </c>
-      <c r="M2" s="3">
-        <f>ROUND(ROUND(L2*4, 0)*0.8, 0)</f>
+      <c r="F15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14">
+        <f t="shared" ref="D16:D18" si="5">HOUR(C16-B16)*60 + MINUTE(C16-B16)</f>
         <v>0</v>
       </c>
-      <c r="N2">
+      <c r="E16" s="15">
+        <f t="shared" ref="E16:E18" si="6">ROUND(ROUND(D16*4, 0)*0.8, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="14" t="e">
-        <f t="shared" ref="B3:B8" si="3">ROUNDUP(G3*1.6, 0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E3" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="4">
-        <f t="shared" ref="L3:L5" si="4">HOUR(K3-J3)*60 + MINUTE(K3-J3)</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <f t="shared" ref="M3:M5" si="5">ROUND(ROUND(L3*4, 0)*0.8, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="14" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E4" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="E17" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="14" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E5" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N5">
+      <c r="E18" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="14" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E6" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="14" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E7" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="14" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="14"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="21"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="14" t="e">
-        <f>ROUNDUP(G11*1.6, 0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="18" t="e">
-        <f t="shared" ref="D11" si="6">VLOOKUP(VALUE(LEFT(C11,1)),$I$2:$J$7,2,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" s="18" t="e">
-        <f t="shared" ref="E11" si="7">VLOOKUP(VALUE(RIGHT(C11,1)),$I$2:$K$7,3,FALSE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="21" t="e">
-        <f t="shared" ref="G11" si="8">HOUR(E11-D11)*60 + MINUTE(E11-D11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="14"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="21"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="16" t="e">
-        <f>M13-SUM(B2:B9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M13" s="13">
-        <f>SUM(M2:M9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G14" s="20"/>
-      <c r="H14" s="3" t="e">
-        <f>H13-B11</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="4"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="4"/>
-      <c r="G16" s="20"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="I18" s="4"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
+    <sheet name="0807" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Гравець</t>
   </si>
@@ -43,35 +44,62 @@
     <t>Пушняк</t>
   </si>
   <si>
-    <t>Козин</t>
-  </si>
-  <si>
     <t>Воронцов</t>
   </si>
   <si>
-    <t>Розовецький</t>
-  </si>
-  <si>
     <t>Москаленко</t>
   </si>
   <si>
     <t>Мілевський</t>
   </si>
   <si>
-    <t>Ганушевич</t>
-  </si>
-  <si>
     <t>Хомін</t>
   </si>
   <si>
     <t>0 - 0</t>
+  </si>
+  <si>
+    <t>4 - 4</t>
+  </si>
+  <si>
+    <t>4 -</t>
+  </si>
+  <si>
+    <t>7 - 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 7</t>
+  </si>
+  <si>
+    <t>6 - 7</t>
+  </si>
+  <si>
+    <t>Галайдюк</t>
+  </si>
+  <si>
+    <t>7 - 7</t>
+  </si>
+  <si>
+    <t>19:16</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>20:11</t>
+  </si>
+  <si>
+    <t>20:56</t>
+  </si>
+  <si>
+    <t>19:12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,8 +126,28 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,8 +166,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -187,11 +247,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -239,9 +360,57 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -541,7 +710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист75"/>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -573,14 +742,14 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1" s="9" t="e">
         <f>ROUNDUP(O1*1.6, 0)</f>
         <v>#N/A</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L1" s="6" t="e">
         <f>VLOOKUP(VALUE(LEFT(K1,1)),$A$15:$B$20,2,FALSE)</f>
@@ -597,141 +766,112 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
       <c r="B2" s="9" t="e">
         <f>ROUNDUP(G2*1.6, 0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C2" s="20"/>
       <c r="D2" s="6" t="e">
         <f>VLOOKUP(VALUE(LEFT(C2,1)),$A$15:$B$20,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E2" s="6" t="e">
         <f>VLOOKUP(VALUE(RIGHT(C2,1)),$A$15:$C$20,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="11" t="e">
         <f t="shared" ref="G2:G8" si="1">HOUR(E2-D2)*60 + MINUTE(E2-D2)</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="N2" s="14" t="e">
-        <f>I3-SUM(B2:B11)</f>
-        <v>#N/A</v>
+        <f>E22-SUM(B2:B11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
       <c r="B3" s="9" t="e">
         <f t="shared" ref="B3:B8" si="2">ROUNDUP(G3*1.6, 0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C3" s="20"/>
       <c r="D3" s="6" t="e">
         <f t="shared" ref="D3:D8" si="3">VLOOKUP(VALUE(LEFT(C3,1)),$A$15:$B$20,2,FALSE)</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E3" s="6" t="e">
         <f t="shared" ref="E3:E8" si="4">VLOOKUP(VALUE(RIGHT(C3,1)),$A$15:$C$20,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H3" s="16"/>
-      <c r="I3" s="9">
-        <f>SUM(E15:E20)</f>
-        <v>0</v>
-      </c>
       <c r="N3" s="9" t="e">
         <f>N2-J1</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
       <c r="B4" s="9" t="e">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="20"/>
       <c r="D4" s="6" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E4" s="6" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
       <c r="B5" s="9" t="e">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="20"/>
       <c r="D5" s="6" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E5" s="6" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
       <c r="B6" s="9" t="e">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" s="20"/>
       <c r="D6" s="6" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="6" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="17"/>
@@ -741,28 +881,23 @@
       <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
       <c r="B7" s="9" t="e">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="20"/>
       <c r="D7" s="6" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E7" s="6" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="17"/>
@@ -772,28 +907,23 @@
       <c r="N7" s="18"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
       <c r="B8" s="9" t="e">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>16</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="20"/>
       <c r="D8" s="6" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="6" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="17"/>
@@ -887,7 +1017,9 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
+      <c r="A15" s="12">
+        <v>4</v>
+      </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
       <c r="D15" s="14">
@@ -903,7 +1035,9 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="12">
+        <v>6</v>
+      </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="14">
@@ -919,7 +1053,9 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+      <c r="A17" s="12">
+        <v>7</v>
+      </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="14">
@@ -935,7 +1071,9 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+      <c r="A18" s="12">
+        <v>3</v>
+      </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="14">
@@ -958,8 +1096,461 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G20" s="19"/>
     </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E22" s="9">
+        <f>SUM(E15:E20)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O98"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" style="28" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="28" customWidth="1"/>
+    <col min="4" max="5" width="7.28515625" style="28" customWidth="1"/>
+    <col min="6" max="7" width="7.7109375" style="28" customWidth="1"/>
+    <col min="8" max="9" width="8.7109375" style="28" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" style="28" customWidth="1"/>
+    <col min="12" max="15" width="8.7109375" style="28" customWidth="1"/>
+    <col min="16" max="16384" width="14.42578125" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="26"/>
+      <c r="G1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="29">
+        <f>ROUNDUP(O1*1.6, 0)</f>
+        <v>247</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="26" t="str">
+        <f>VLOOKUP(VALUE(LEFT(K1,1)),$A$13:$B$17,2,FALSE)</f>
+        <v>19:16</v>
+      </c>
+      <c r="M1" s="26" t="str">
+        <f>VLOOKUP(VALUE(RIGHT(K1,1)),$A$13:$C$17,3,FALSE)</f>
+        <v>21:50</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="31">
+        <f>HOUR(M1-L1)*60 + MINUTE(M1-L1)</f>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="29">
+        <f t="shared" ref="B2:B6" si="0">ROUNDUP(G2*1.6, 0)</f>
+        <v>199</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="26" t="str">
+        <f t="shared" ref="D2:D3" si="1">VLOOKUP(VALUE(LEFT(C2,1)),$A$13:$B$17,2,FALSE)</f>
+        <v>19:16</v>
+      </c>
+      <c r="E2" s="26">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2:G6" si="2">HOUR(E2-D2)*60 + MINUTE(E2-D2)</f>
+        <v>124</v>
+      </c>
+      <c r="N2" s="31">
+        <f>I3-SUM(B2:B9)</f>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="29">
+        <f t="shared" si="0"/>
+        <v>167</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>19:12</v>
+      </c>
+      <c r="E3" s="26" t="str">
+        <f t="shared" ref="E3:E6" si="3">VLOOKUP(VALUE(RIGHT(C3,1)),$A$13:$C$17,3,FALSE)</f>
+        <v>20:56</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="31">
+        <f t="shared" si="2"/>
+        <v>104</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="29">
+        <f>SUM(E13:E17)</f>
+        <v>1143</v>
+      </c>
+      <c r="N3" s="29">
+        <f>N2-J1</f>
+        <v>-106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="29">
+        <f t="shared" si="0"/>
+        <v>224</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="26">
+        <v>0.8125</v>
+      </c>
+      <c r="E4" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>21:50</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="31">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="29">
+        <f t="shared" si="0"/>
+        <v>159</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="26" t="str">
+        <f t="shared" ref="D5:D6" si="4">VLOOKUP(VALUE(LEFT(C5,1)),$A$13:$B$17,2,FALSE)</f>
+        <v>20:11</v>
+      </c>
+      <c r="E5" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>21:50</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="31">
+        <f t="shared" si="2"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="29">
+        <f t="shared" si="0"/>
+        <v>253</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v>19:12</v>
+      </c>
+      <c r="E6" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>21:50</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="31">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="31"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="31"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="29"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="31"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="29"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="31"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="29"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="31"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>4</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="31">
+        <f t="shared" ref="D13:D15" si="5">HOUR(C13-B13)*60 + MINUTE(C13-B13)</f>
+        <v>154</v>
+      </c>
+      <c r="E13" s="40">
+        <f t="shared" ref="E13:E15" si="6">ROUND(ROUND(D13*4, 0)*0.8, 0)</f>
+        <v>493</v>
+      </c>
+      <c r="F13" s="28">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>6</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="31">
+        <f t="shared" si="5"/>
+        <v>45</v>
+      </c>
+      <c r="E14" s="40">
+        <f t="shared" si="6"/>
+        <v>144</v>
+      </c>
+      <c r="F14" s="28">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>7</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="31">
+        <f t="shared" si="5"/>
+        <v>158</v>
+      </c>
+      <c r="E15" s="40">
+        <f t="shared" si="6"/>
+        <v>506</v>
+      </c>
+      <c r="F15" s="28">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="38"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="40"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="41"/>
+    </row>
+    <row r="18" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -1017,9 +1017,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>4</v>
-      </c>
+      <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
       <c r="D15" s="14">
@@ -1035,9 +1033,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>6</v>
-      </c>
+      <c r="A16" s="12"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="14">
@@ -1053,9 +1049,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>7</v>
-      </c>
+      <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="14">
@@ -1071,9 +1065,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <v>3</v>
-      </c>
+      <c r="A18" s="12"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="14">

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,14 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
-    <sheet name="0807" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Гравець</t>
   </si>
@@ -41,65 +40,17 @@
     <t>Тариф</t>
   </si>
   <si>
-    <t>Пушняк</t>
-  </si>
-  <si>
-    <t>Воронцов</t>
-  </si>
-  <si>
-    <t>Москаленко</t>
-  </si>
-  <si>
-    <t>Мілевський</t>
-  </si>
-  <si>
     <t>Хомін</t>
   </si>
   <si>
     <t>0 - 0</t>
-  </si>
-  <si>
-    <t>4 - 4</t>
-  </si>
-  <si>
-    <t>4 -</t>
-  </si>
-  <si>
-    <t>7 - 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 7</t>
-  </si>
-  <si>
-    <t>6 - 7</t>
-  </si>
-  <si>
-    <t>Галайдюк</t>
-  </si>
-  <si>
-    <t>7 - 7</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>20:11</t>
-  </si>
-  <si>
-    <t>20:56</t>
-  </si>
-  <si>
-    <t>19:12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,22 +83,8 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,20 +103,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFBFBF"/>
-        <bgColor rgb="FFBFBFBF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -247,72 +172,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -360,53 +225,6 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -742,14 +560,14 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J1" s="9" t="e">
         <f>ROUNDUP(O1*1.6, 0)</f>
         <v>#N/A</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6" t="e">
         <f>VLOOKUP(VALUE(LEFT(K1,1)),$A$15:$B$20,2,FALSE)</f>
@@ -1098,451 +916,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O98"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" style="28" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="28" customWidth="1"/>
-    <col min="4" max="5" width="7.28515625" style="28" customWidth="1"/>
-    <col min="6" max="7" width="7.7109375" style="28" customWidth="1"/>
-    <col min="8" max="9" width="8.7109375" style="28" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" style="28" customWidth="1"/>
-    <col min="12" max="15" width="8.7109375" style="28" customWidth="1"/>
-    <col min="16" max="16384" width="14.42578125" style="28"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="26"/>
-      <c r="G1" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="29">
-        <f>ROUNDUP(O1*1.6, 0)</f>
-        <v>247</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="26" t="str">
-        <f>VLOOKUP(VALUE(LEFT(K1,1)),$A$13:$B$17,2,FALSE)</f>
-        <v>19:16</v>
-      </c>
-      <c r="M1" s="26" t="str">
-        <f>VLOOKUP(VALUE(RIGHT(K1,1)),$A$13:$C$17,3,FALSE)</f>
-        <v>21:50</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="31">
-        <f>HOUR(M1-L1)*60 + MINUTE(M1-L1)</f>
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="29">
-        <f t="shared" ref="B2:B6" si="0">ROUNDUP(G2*1.6, 0)</f>
-        <v>199</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="26" t="str">
-        <f t="shared" ref="D2:D3" si="1">VLOOKUP(VALUE(LEFT(C2,1)),$A$13:$B$17,2,FALSE)</f>
-        <v>19:16</v>
-      </c>
-      <c r="E2" s="26">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G6" si="2">HOUR(E2-D2)*60 + MINUTE(E2-D2)</f>
-        <v>124</v>
-      </c>
-      <c r="N2" s="31">
-        <f>I3-SUM(B2:B9)</f>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="29">
-        <f t="shared" si="0"/>
-        <v>167</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>19:12</v>
-      </c>
-      <c r="E3" s="26" t="str">
-        <f t="shared" ref="E3:E6" si="3">VLOOKUP(VALUE(RIGHT(C3,1)),$A$13:$C$17,3,FALSE)</f>
-        <v>20:56</v>
-      </c>
-      <c r="F3" s="26"/>
-      <c r="G3" s="31">
-        <f t="shared" si="2"/>
-        <v>104</v>
-      </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="29">
-        <f>SUM(E13:E17)</f>
-        <v>1143</v>
-      </c>
-      <c r="N3" s="29">
-        <f>N2-J1</f>
-        <v>-106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="29">
-        <f t="shared" si="0"/>
-        <v>224</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="26">
-        <v>0.8125</v>
-      </c>
-      <c r="E4" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>21:50</v>
-      </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="31">
-        <f t="shared" si="2"/>
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="29">
-        <f t="shared" si="0"/>
-        <v>159</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="26" t="str">
-        <f t="shared" ref="D5:D6" si="4">VLOOKUP(VALUE(LEFT(C5,1)),$A$13:$B$17,2,FALSE)</f>
-        <v>20:11</v>
-      </c>
-      <c r="E5" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>21:50</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="31">
-        <f t="shared" si="2"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="29">
-        <f t="shared" si="0"/>
-        <v>253</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v>19:12</v>
-      </c>
-      <c r="E6" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>21:50</v>
-      </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="31">
-        <f t="shared" si="2"/>
-        <v>158</v>
-      </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="31"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="31"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="31"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="31"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="31"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="38">
-        <v>4</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="31">
-        <f t="shared" ref="D13:D15" si="5">HOUR(C13-B13)*60 + MINUTE(C13-B13)</f>
-        <v>154</v>
-      </c>
-      <c r="E13" s="40">
-        <f t="shared" ref="E13:E15" si="6">ROUND(ROUND(D13*4, 0)*0.8, 0)</f>
-        <v>493</v>
-      </c>
-      <c r="F13" s="28">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="38">
-        <v>6</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="31">
-        <f t="shared" si="5"/>
-        <v>45</v>
-      </c>
-      <c r="E14" s="40">
-        <f t="shared" si="6"/>
-        <v>144</v>
-      </c>
-      <c r="F14" s="28">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="38">
-        <v>7</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="31">
-        <f t="shared" si="5"/>
-        <v>158</v>
-      </c>
-      <c r="E15" s="40">
-        <f t="shared" si="6"/>
-        <v>506</v>
-      </c>
-      <c r="F15" s="28">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="38"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="40"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="41"/>
-    </row>
-    <row r="18" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>